--- a/Excel/ThucTich_Data.xlsx
+++ b/Excel/ThucTich_Data.xlsx
@@ -1,89 +1,220 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code_cokhi\Bao_Cao_Tu_Dong_PPTX_New\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FA2FEB-8D69-4B73-8251-7EA1FD0D895C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>Tháng</t>
+  </si>
+  <si>
+    <t>Thực tích Bản vẽ hoàn thành</t>
+  </si>
+  <si>
+    <t>Thực tích PCS hoàn thành</t>
+  </si>
+  <si>
+    <t>Bản vẽ Hoàn thành, Trễ hẹn và Phụ tải công đoạn - 2026-04-09</t>
+  </si>
+  <si>
+    <t>1月</t>
+  </si>
+  <si>
+    <t>Công đoạn</t>
+  </si>
+  <si>
+    <t>Phụ tải Công đoạn (Hiện tại)</t>
+  </si>
+  <si>
+    <t>Phụ tải Công đoạn (Tổng)</t>
+  </si>
+  <si>
+    <t>Số bản vẽ trễ hẹn</t>
+  </si>
+  <si>
+    <t>Số bản vẽ Hoàn thành</t>
+  </si>
+  <si>
+    <t>Hiệu suất (Ngày)</t>
+  </si>
+  <si>
+    <t>2月</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>3月</t>
+  </si>
+  <si>
+    <t>BJ</t>
+  </si>
+  <si>
+    <t>4月</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>5月</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>6月</t>
+  </si>
+  <si>
+    <t>EW</t>
+  </si>
+  <si>
+    <t>7月</t>
+  </si>
+  <si>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>8月</t>
+  </si>
+  <si>
+    <t>GJ</t>
+  </si>
+  <si>
+    <t>9月</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
+    <t>10月</t>
+  </si>
+  <si>
+    <t>GR</t>
+  </si>
+  <si>
+    <t>11月</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>12月</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>LN</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF2C3E50"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF2C3E50"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -130,133 +261,54 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -522,491 +574,416 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet1">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="17.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="17.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="6.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="17" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="14" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="2.109375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.33203125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="17" bestFit="1" customWidth="1" min="8" max="9"/>
-    <col width="18.88671875" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="17.5546875" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tháng</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Thực tích Bản vẽ hoàn thành</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Thực tích PCS hoàn thành</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>Bản vẽ Hoàn thành, Trễ hẹn và Phụ tải công đoạn - 2026-04-09</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="n"/>
-      <c r="I1" s="9" t="n"/>
-      <c r="J1" s="9" t="n"/>
-      <c r="K1" s="9" t="n"/>
-      <c r="L1" s="10" t="n"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
+    <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2">
         <v>2420</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>34743</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Công đoạn</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Phụ tải Công đoạn (Hiện tại)</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Phụ tải Công đoạn (Tổng)</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>Số bản vẽ trễ hẹn</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>Số bản vẽ Hoàn thành</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>Hiệu suất (Ngày)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2">
         <v>1572</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>19982</v>
       </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>AF</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n">
+      <c r="G3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="5">
         <v>5.53</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="5">
         <v>59.09</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="3">
         <v>119</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="K3" s="6">
         <v>41</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="5">
         <v>39.11</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2">
         <v>2309</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2">
         <v>35509</v>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>BJ</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="n">
+      <c r="G4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="6">
         <v>7.77</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="6">
         <v>39.72</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="3">
         <v>97</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="6">
         <v>46</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="6">
         <v>61.53</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>4月</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2">
         <v>735</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="2">
         <v>10314</v>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>DA</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="G5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="6">
         <v>0.02</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="6">
         <v>12.71</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="3">
         <v>19</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="6">
         <v>17</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="6">
         <v>51.15</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5月</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="G6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="6">
         <v>5.56</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="6">
         <v>45.83</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="3">
         <v>42</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="6">
         <v>8</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="6">
         <v>25.49</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6月</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="G7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="6">
         <v>32.47</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="6">
         <v>76.67</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="3">
         <v>55</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="6">
         <v>18</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="6">
         <v>21.62</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7月</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="G8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="6">
         <v>48.54</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="6">
         <v>84.31</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="3">
         <v>22</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="6">
         <v>7</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="6">
         <v>67.95</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>8月</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>GJ</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="G9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="6">
         <v>2.8</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>32.91</v>
-      </c>
-      <c r="J9" s="3" t="n">
+      <c r="I9" s="6">
+        <v>32.909999999999997</v>
+      </c>
+      <c r="J9" s="3">
         <v>12</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="K9" s="6">
         <v>5</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="L9" s="6">
         <v>32.28</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>9月</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>GP</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="n">
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="G10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="6">
         <v>7.56</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="6">
         <v>46.09</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" s="3">
         <v>33</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="6">
         <v>11</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="6">
         <v>63.07</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>10月</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="6">
         <v>19.05</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="6">
         <v>49.89</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" s="3">
         <v>35</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="6">
         <v>11</v>
       </c>
-      <c r="L11" s="6" t="n">
-        <v>66.93000000000001</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>11月</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="L11" s="6">
+        <v>66.930000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="G12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="6">
         <v>10.99</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="6">
         <v>43.95</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="3">
         <v>117</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="6">
         <v>51</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="6">
         <v>75.97</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12月</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="G13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="6">
         <v>24.24</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="6">
         <v>27.71</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="3">
         <v>66</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K13" s="6">
         <v>13</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="6">
         <v>63.43</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="6">
         <v>57.94</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="6">
         <v>84.66</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="3">
         <v>33</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="6">
         <v>5</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="6">
         <v>25.1</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="6">
         <v>11.18</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="6">
         <v>26.38</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="3">
         <v>63</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" s="6">
         <v>49</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="6">
         <v>53.78</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>MC</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="6">
         <v>25.24</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="6">
         <v>60.79</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" s="3">
         <v>50</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="6">
         <v>11</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="6">
         <v>45.53</v>
       </c>
     </row>
